--- a/py_src/쿼리추출/소스타겟정리과정.xlsx
+++ b/py_src/쿼리추출/소스타겟정리과정.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="sql_est_srctgt_013.py" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="with포함시요청해야 할 내용" sheetId="9" r:id="rId7"/>
     <sheet name="구현과정" sheetId="10" r:id="rId8"/>
     <sheet name="sql_lng_002.py" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="1590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="1626">
   <si>
     <t>이미지에서 파악한 내용:</t>
   </si>
@@ -10011,12 +10012,729 @@
     <t>tgt_table</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>테이블단위 리니지 할 경우 cte 테이블 cte_1,cte_2,cte_3의 3개를 생성하고</t>
+  </si>
+  <si>
+    <t>3개(cte_1,cte_2,cte_3)를 소스로 cte_4 cte테이블을 생성하고</t>
+  </si>
+  <si>
+    <t>최종 cte_1,cte_2,cte_3, cte_4를 이용 최종 테이블 tb에 insert하는 경우</t>
+  </si>
+  <si>
+    <t>"3개(cte_1,cte_2,cte_3)를 소스로 cte_4 cte테이블을 생성"하는 부분은 표현이 안되어도 되는지?</t>
+  </si>
+  <si>
+    <t>Gemini의 응답</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">결론부터 말씀드리면, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>추출의 목적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 따라 답이 달라집니다. 하지만 일반적으로 "테이블 단위 리니지"를 구축할 때는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 생성 과정도 포함하는 것이 훨씬 정확한 분석 데이터를 제공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>합니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>구체적인 이유와 상황별 판단 기준을 정리해 드립니다.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 생성 과정을 포함해야 하는 이유 (권장)</t>
+    </r>
+  </si>
+  <si>
+    <t>리니지(Lineage)의 핵심은 데이터가 어떤 경로를 거쳐 변형되었는지 기록하는 것입니다.</t>
+  </si>
+  <si>
+    <r>
+      <t>영향도 분석 (Impact Analysis):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 만약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 테이블의 로직이 변경되었을 때, 이 변경이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>tb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 직접 영향을 주는지 아니면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>라는 중간 단계를 거쳐 영향을 주는지 파악해야 합니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>복잡성 파악:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>tb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 테이블이 단순히 3개에서 오는 것이 아니라, 중간에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>라는 집계/가공 단계를 거친다는 사실 자체가 데이터의 복잡성을 나타내는 중요한 정보입니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>데이터 정합성 추적:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 최종 결과물 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>tb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 이상이 생겼을 때, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_1~3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 문제인지 아니면 이들을 합친 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 로직의 문제인지 단계를 나누어 추적할 수 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. 표현하지 않아도 되는 경우 (예외)</t>
+  </si>
+  <si>
+    <t>만약 리니지의 목적이 **"최종 물리 테이블 간의 관계"**에만 집중되어 있다면 생략하기도 합니다.</t>
+  </si>
+  <si>
+    <r>
+      <t>물리적 관계 중심:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 중간 과정(CTE, Temp Table)은 메모리상에서만 존재하므로, "결국 어떤 물리 테이블이 어떤 물리 테이블로 들어갔는가"만 중요하다면 생략할 수 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>단순화 모드:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SIMPLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 모드처럼 사용자가 내부 로직보다는 소스(Source)와 타겟(Target)의 직결 관계만 보고 싶어 할 때입니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. 추천하는 리니지 구성 방식 (Table Level)</t>
+  </si>
+  <si>
+    <t>가장 이상적인 형태는 아래와 같이 **Depth(단계)**를 두어 모두 표현하는 것입니다.</t>
+  </si>
+  <si>
+    <t>단계 (Depth)</t>
+  </si>
+  <si>
+    <t>소스 (Source)</t>
+  </si>
+  <si>
+    <t>타겟 (Target)</t>
+  </si>
+  <si>
+    <t>유형</t>
+  </si>
+  <si>
+    <r>
+      <t>S1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>S2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>S3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cte_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_3</t>
+    </r>
+  </si>
+  <si>
+    <t>CTE 생성</t>
+  </si>
+  <si>
+    <t>cte_4</t>
+  </si>
+  <si>
+    <t>중간 가공</t>
+  </si>
+  <si>
+    <r>
+      <t>cte_1, 2, 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+  </si>
+  <si>
+    <t>tb</t>
+  </si>
+  <si>
+    <t>최종 적재</t>
+  </si>
+  <si>
+    <t>4. 현재 소스 코드에서의 처리 팁</t>
+  </si>
+  <si>
+    <t>작성 중이신 파이썬 스크립트에서 이 부분을 어떻게 처리할지 결정하셔야 합니다.</t>
+  </si>
+  <si>
+    <r>
+      <t>1. DETAIL 모드:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 생성하는 과정을 레코드로 남깁니다. (소스: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_1,2,3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; 타겟: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. SIMPLE 모드:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 무시하고, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>가 참조하는 원천 소스들(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>S1, S2...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)이 바로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>tb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>로 가는 것으로 계산(Recursive Trace)하여 출력합니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>💡 한 줄 요약:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 데이터의 흐름을 정확히 관리하고 싶다면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_1,2,3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 단계를 반드시 리니지에 포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>시키는 것을 추천합니다. 그래야만 나중에 로직이 바뀌었을 때 "어디서 데이터가 틀어졌는지" 정확히 찾아낼 수 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">혹시 지금 작성 중인 코드에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cte_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>가 누락되어 나오나요? 그렇다면 CTE 맵을 추출하는 재귀 로직을 점검해 드릴 수 있습니다. 어떻게 도와드릴까요?</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10167,8 +10885,47 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10184,6 +10941,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10217,7 +10980,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10334,6 +11097,30 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10768,6 +11555,316 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="39" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="39" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="39" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="39" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4" ht="26.25">
+      <c r="A5" s="13" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="39" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="39" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" ht="19.5">
+      <c r="A10" s="40" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="39" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="42" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="42" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="42" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4" ht="19.5">
+      <c r="A17" s="40" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="39" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="42" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="42" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" ht="19.5">
+      <c r="A23" s="40" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="39" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" ht="28.5">
+      <c r="A25" s="43" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="45">
+      <c r="A26" s="44">
+        <v>1</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="45">
+      <c r="A27" s="44">
+        <v>2</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="45">
+      <c r="A28" s="44">
+        <v>3</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" ht="19.5">
+      <c r="A31" s="40" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="39" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="42" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="42" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="41" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="39" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C27"/>
